--- a/prix/tube-alpex.xlsx
+++ b/prix/tube-alpex.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BB0D4D-B24F-4D04-BCB0-877A711C9548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D307DA4F-F730-410D-ACE8-9A6BFB44EE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{4E6DADB0-7397-45D0-B450-49581E83838D}"/>
   </bookViews>
@@ -265,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -289,9 +289,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -300,6 +297,12 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -642,7 +645,7 @@
     <col min="2" max="2" width="29.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5546875" style="7"/>
     <col min="4" max="5" width="11.5546875" style="6"/>
-    <col min="6" max="6" width="22.77734375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="22.77734375" style="11" customWidth="1"/>
     <col min="7" max="7" width="51.77734375" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.77734375" style="2" customWidth="1"/>
     <col min="9" max="9" width="23.77734375" style="1" customWidth="1"/>
@@ -667,7 +670,7 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>56</v>
       </c>
       <c r="G1" s="1"/>
@@ -689,14 +692,14 @@
       <c r="C2" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="13">
         <v>96.15</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="12">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -709,14 +712,14 @@
       <c r="C3" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="13">
         <v>88.9</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F3" s="12">
-        <v>2.8</v>
+        <v>4.8000000000000025</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -729,14 +732,14 @@
       <c r="C4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="9">
-        <v>141.72</v>
+      <c r="D4" s="13">
+        <v>106.87</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -749,14 +752,14 @@
       <c r="C5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="9">
-        <v>141.72</v>
+      <c r="D5" s="13">
+        <v>111.32000000000001</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="12">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -769,7 +772,7 @@
       <c r="C6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="13">
         <v>63.08</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -789,14 +792,14 @@
       <c r="C7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="13">
         <v>63.08</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -809,14 +812,14 @@
       <c r="C8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="13">
         <v>2.0100000000000002</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>29</v>
       </c>
       <c r="F8" s="12">
-        <v>468</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -829,14 +832,14 @@
       <c r="C9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="13">
         <v>3.75</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>30</v>
       </c>
       <c r="F9" s="12">
-        <v>315</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -849,14 +852,14 @@
       <c r="C10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="13">
         <v>7.07</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="12">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -869,7 +872,7 @@
       <c r="C11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="13">
         <v>12.61</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -889,7 +892,7 @@
       <c r="C12" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="13">
         <v>8.65</v>
       </c>
       <c r="E12" s="8" t="s">
@@ -909,7 +912,7 @@
       <c r="C13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="13">
         <v>208.51</v>
       </c>
       <c r="E13" s="8" t="s">
@@ -929,7 +932,7 @@
       <c r="C14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="13">
         <v>157.20000000000002</v>
       </c>
       <c r="E14" s="8" t="s">
@@ -949,7 +952,7 @@
       <c r="C15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="13">
         <v>67.8</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -969,7 +972,7 @@
       <c r="C16" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="13">
         <v>106.87</v>
       </c>
       <c r="E16" s="8" t="s">
@@ -989,8 +992,8 @@
       <c r="C17" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="9">
-        <v>70.37</v>
+      <c r="D17" s="13">
+        <v>66.790000000000006</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>38</v>
@@ -1009,7 +1012,7 @@
       <c r="C18" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="13">
         <v>106.87</v>
       </c>
       <c r="E18" s="8" t="s">
@@ -1029,7 +1032,7 @@
       <c r="C19" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="13">
         <v>158.75</v>
       </c>
       <c r="E19" s="8" t="s">
@@ -1049,10 +1052,10 @@
       <c r="C20" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="13">
         <v>3.17</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <v>43123020</v>
       </c>
       <c r="F20" s="12">

--- a/prix/tube-alpex.xlsx
+++ b/prix/tube-alpex.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D307DA4F-F730-410D-ACE8-9A6BFB44EE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56083B3-61EF-4866-B1E7-02A6C2626D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{4E6DADB0-7397-45D0-B450-49581E83838D}"/>
   </bookViews>
@@ -298,10 +298,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -692,14 +692,14 @@
       <c r="C2" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="13">
-        <v>96.15</v>
+      <c r="D2" s="12">
+        <v>76.790000000000006</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="12">
-        <v>3</v>
+      <c r="F2" s="13">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -712,14 +712,14 @@
       <c r="C3" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="13">
-        <v>88.9</v>
+      <c r="D3" s="12">
+        <v>76.790000000000006</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="12">
-        <v>4.8000000000000025</v>
+      <c r="F3" s="13">
+        <v>14.800000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -732,14 +732,14 @@
       <c r="C4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>106.87</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="12">
-        <v>3</v>
+      <c r="F4" s="13">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -752,13 +752,13 @@
       <c r="C5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="13">
-        <v>111.32000000000001</v>
+      <c r="D5" s="12">
+        <v>106.87</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <v>4</v>
       </c>
     </row>
@@ -772,14 +772,14 @@
       <c r="C6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="13">
-        <v>63.08</v>
+      <c r="D6" s="12">
+        <v>76.790000000000006</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="12">
-        <v>0</v>
+      <c r="F6" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -792,14 +792,14 @@
       <c r="C7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="13">
-        <v>63.08</v>
+      <c r="D7" s="12">
+        <v>76.790000000000006</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="12">
-        <v>0</v>
+      <c r="F7" s="13">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -812,14 +812,14 @@
       <c r="C8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <v>2.0100000000000002</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="12">
-        <v>445</v>
+      <c r="F8" s="13">
+        <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -832,14 +832,14 @@
       <c r="C9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <v>3.75</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="12">
-        <v>295</v>
+      <c r="F9" s="13">
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -852,14 +852,14 @@
       <c r="C10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="12">
         <v>7.07</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="12">
-        <v>84</v>
+      <c r="F10" s="13">
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -872,13 +872,13 @@
       <c r="C11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="13">
-        <v>12.61</v>
+      <c r="D11" s="12">
+        <v>12.200000000000001</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <v>0</v>
       </c>
     </row>
@@ -892,13 +892,13 @@
       <c r="C12" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="13">
-        <v>8.65</v>
+      <c r="D12" s="12">
+        <v>8.35</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <v>0</v>
       </c>
     </row>
@@ -912,13 +912,13 @@
       <c r="C13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <v>208.51</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>1</v>
       </c>
     </row>
@@ -932,13 +932,13 @@
       <c r="C14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="12">
         <v>157.20000000000002</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <v>3</v>
       </c>
     </row>
@@ -952,14 +952,14 @@
       <c r="C15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="13">
-        <v>67.8</v>
+      <c r="D15" s="12">
+        <v>53.43</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="12">
-        <v>1.9999999999999876</v>
+      <c r="F15" s="13">
+        <v>-1.0000000000000124</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -972,13 +972,13 @@
       <c r="C16" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="12">
         <v>106.87</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <v>3.0000000000000133</v>
       </c>
     </row>
@@ -992,13 +992,13 @@
       <c r="C17" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="13">
-        <v>66.790000000000006</v>
+      <c r="D17" s="12">
+        <v>53.43</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <v>-1.2434497875801753E-14</v>
       </c>
     </row>
@@ -1012,14 +1012,14 @@
       <c r="C18" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <v>106.87</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="12">
-        <v>5.0000000000000213</v>
+      <c r="F18" s="13">
+        <v>2.600000000000021</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1032,14 +1032,14 @@
       <c r="C19" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="12">
         <v>158.75</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="12">
-        <v>250</v>
+      <c r="F19" s="13">
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1052,13 +1052,13 @@
       <c r="C20" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="12">
         <v>3.17</v>
       </c>
       <c r="E20" s="9">
         <v>43123020</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="13">
         <v>0</v>
       </c>
     </row>

--- a/prix/tube-alpex.xlsx
+++ b/prix/tube-alpex.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56083B3-61EF-4866-B1E7-02A6C2626D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5734152B-A241-4BA1-B718-70876F262154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{4E6DADB0-7397-45D0-B450-49581E83838D}"/>
   </bookViews>
@@ -819,7 +819,7 @@
         <v>29</v>
       </c>
       <c r="F8" s="13">
-        <v>354</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -899,7 +899,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="13">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -979,7 +979,7 @@
         <v>37</v>
       </c>
       <c r="F16" s="13">
-        <v>3.0000000000000133</v>
+        <v>2.0000000000000133</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/tube-alpex.xlsx
+++ b/prix/tube-alpex.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5734152B-A241-4BA1-B718-70876F262154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A1DCFA-278D-49EF-9BC9-F601CBC69145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{4E6DADB0-7397-45D0-B450-49581E83838D}"/>
   </bookViews>
@@ -819,7 +819,7 @@
         <v>29</v>
       </c>
       <c r="F8" s="13">
-        <v>321</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -839,7 +839,7 @@
         <v>30</v>
       </c>
       <c r="F9" s="13">
-        <v>224</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -859,7 +859,7 @@
         <v>31</v>
       </c>
       <c r="F10" s="13">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1019,7 +1019,7 @@
         <v>39</v>
       </c>
       <c r="F18" s="13">
-        <v>2.600000000000021</v>
+        <v>1.600000000000021</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">

--- a/prix/tube-alpex.xlsx
+++ b/prix/tube-alpex.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A1DCFA-278D-49EF-9BC9-F601CBC69145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9690A0C3-6F2B-4788-B509-61BAC9B479A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{4E6DADB0-7397-45D0-B450-49581E83838D}"/>
   </bookViews>
@@ -719,7 +719,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="13">
-        <v>14.800000000000002</v>
+        <v>12.800000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -739,7 +739,7 @@
         <v>25</v>
       </c>
       <c r="F4" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -759,7 +759,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -819,7 +819,7 @@
         <v>29</v>
       </c>
       <c r="F8" s="13">
-        <v>71</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -839,7 +839,7 @@
         <v>30</v>
       </c>
       <c r="F9" s="13">
-        <v>189</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -859,7 +859,7 @@
         <v>31</v>
       </c>
       <c r="F10" s="13">
-        <v>64</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -979,7 +979,7 @@
         <v>37</v>
       </c>
       <c r="F16" s="13">
-        <v>2.0000000000000133</v>
+        <v>4.0000000000000133</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1019,7 +1019,7 @@
         <v>39</v>
       </c>
       <c r="F18" s="13">
-        <v>1.600000000000021</v>
+        <v>4.600000000000021</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1039,7 +1039,7 @@
         <v>40</v>
       </c>
       <c r="F19" s="13">
-        <v>249</v>
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
